--- a/KatalonData/RADTestData/EL-NumberValidation.xlsx
+++ b/KatalonData/RADTestData/EL-NumberValidation.xlsx
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="894" uniqueCount="202">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1008" uniqueCount="259">
   <si>
     <t>Result</t>
   </si>
@@ -643,6 +643,177 @@
   </si>
   <si>
     <t>Thu Jul 09 22:33:03 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 00:16:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 00:16:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 00:17:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 00:17:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 00:17:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 00:18:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 00:19:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 00:19:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 00:19:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 00:20:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 00:20:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 00:21:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 00:21:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 00:22:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 00:22:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 00:23:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 00:23:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 00:24:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 00:24:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 00:25:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 00:25:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 00:26:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 00:26:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 00:26:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 00:27:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 00:27:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 00:28:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 00:28:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 00:29:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 00:29:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 00:30:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 00:30:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 00:31:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 00:31:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 00:31:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 00:32:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 00:33:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 00:33:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 00:34:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 00:34:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 00:35:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 00:35:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 00:36:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 00:36:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 00:36:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 00:37:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 00:39:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 00:39:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 00:40:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 00:40:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 00:41:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 00:41:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 00:42:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 00:42:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 00:43:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 00:44:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 00:44:38 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -1055,7 +1226,7 @@
         <v>84</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>145</v>
+        <v>202</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>10</v>
@@ -1078,7 +1249,7 @@
         <v>84</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>146</v>
+        <v>203</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>10</v>
@@ -1101,7 +1272,7 @@
         <v>84</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>147</v>
+        <v>204</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>10</v>
@@ -1124,7 +1295,7 @@
         <v>84</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>148</v>
+        <v>205</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>10</v>
@@ -1147,7 +1318,7 @@
         <v>84</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>149</v>
+        <v>206</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>10</v>
@@ -1170,7 +1341,7 @@
         <v>84</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>150</v>
+        <v>207</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>10</v>
@@ -1193,7 +1364,7 @@
         <v>84</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>151</v>
+        <v>208</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>10</v>
@@ -1216,7 +1387,7 @@
         <v>84</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>152</v>
+        <v>209</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>10</v>
@@ -1239,7 +1410,7 @@
         <v>84</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>153</v>
+        <v>210</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>10</v>
@@ -1262,7 +1433,7 @@
         <v>84</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>154</v>
+        <v>211</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>10</v>
@@ -1285,7 +1456,7 @@
         <v>84</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>155</v>
+        <v>212</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>10</v>
@@ -1308,7 +1479,7 @@
         <v>84</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>156</v>
+        <v>213</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>10</v>
@@ -1331,7 +1502,7 @@
         <v>84</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>157</v>
+        <v>214</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>10</v>
@@ -1354,7 +1525,7 @@
         <v>84</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>158</v>
+        <v>215</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>10</v>
@@ -1377,7 +1548,7 @@
         <v>84</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>159</v>
+        <v>216</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>10</v>
@@ -1400,7 +1571,7 @@
         <v>84</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>160</v>
+        <v>217</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>10</v>
@@ -1423,7 +1594,7 @@
         <v>84</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>161</v>
+        <v>218</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>10</v>
@@ -1446,7 +1617,7 @@
         <v>84</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>162</v>
+        <v>219</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>10</v>
@@ -1469,7 +1640,7 @@
         <v>84</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>163</v>
+        <v>220</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>10</v>
@@ -1492,7 +1663,7 @@
         <v>84</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>164</v>
+        <v>221</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>10</v>
@@ -1515,7 +1686,7 @@
         <v>84</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>165</v>
+        <v>222</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>10</v>
@@ -1538,7 +1709,7 @@
         <v>84</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>166</v>
+        <v>223</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>10</v>
@@ -1561,7 +1732,7 @@
         <v>84</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>167</v>
+        <v>224</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>10</v>
@@ -1584,7 +1755,7 @@
         <v>84</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>168</v>
+        <v>225</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>10</v>
@@ -1607,7 +1778,7 @@
         <v>84</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>169</v>
+        <v>226</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>10</v>
@@ -1630,7 +1801,7 @@
         <v>84</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>170</v>
+        <v>227</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>10</v>
@@ -1653,7 +1824,7 @@
         <v>84</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>171</v>
+        <v>228</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>10</v>
@@ -1676,7 +1847,7 @@
         <v>84</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>172</v>
+        <v>229</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>10</v>
@@ -1699,7 +1870,7 @@
         <v>84</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>173</v>
+        <v>230</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>10</v>
@@ -1722,7 +1893,7 @@
         <v>84</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>174</v>
+        <v>231</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>10</v>
@@ -1745,7 +1916,7 @@
         <v>84</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>175</v>
+        <v>232</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>10</v>
@@ -1768,7 +1939,7 @@
         <v>84</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>176</v>
+        <v>233</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>10</v>
@@ -1791,7 +1962,7 @@
         <v>84</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>177</v>
+        <v>234</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>10</v>
@@ -1814,7 +1985,7 @@
         <v>84</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>178</v>
+        <v>235</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>10</v>
@@ -1837,7 +2008,7 @@
         <v>84</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>179</v>
+        <v>236</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>10</v>
@@ -1860,7 +2031,7 @@
         <v>84</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>180</v>
+        <v>237</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>10</v>
@@ -1883,7 +2054,7 @@
         <v>84</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>181</v>
+        <v>238</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>10</v>
@@ -1906,7 +2077,7 @@
         <v>84</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>182</v>
+        <v>239</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>10</v>
@@ -1929,7 +2100,7 @@
         <v>84</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>183</v>
+        <v>240</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>10</v>
@@ -2003,7 +2174,7 @@
         <v>84</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>184</v>
+        <v>241</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>10</v>
@@ -2026,7 +2197,7 @@
         <v>84</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>185</v>
+        <v>242</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>10</v>
@@ -2049,7 +2220,7 @@
         <v>84</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>186</v>
+        <v>243</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>10</v>
@@ -2072,7 +2243,7 @@
         <v>84</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>187</v>
+        <v>244</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>10</v>
@@ -2095,7 +2266,7 @@
         <v>84</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>188</v>
+        <v>245</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>10</v>
@@ -2118,7 +2289,7 @@
         <v>84</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>189</v>
+        <v>246</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>10</v>
@@ -2141,7 +2312,7 @@
         <v>84</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>190</v>
+        <v>247</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>10</v>
@@ -2164,7 +2335,7 @@
         <v>84</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>191</v>
+        <v>248</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>10</v>
@@ -2187,7 +2358,7 @@
         <v>84</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>192</v>
+        <v>249</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>10</v>
@@ -2210,7 +2381,7 @@
         <v>84</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>193</v>
+        <v>250</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>10</v>
@@ -2233,7 +2404,7 @@
         <v>84</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>194</v>
+        <v>251</v>
       </c>
       <c r="C54" s="2" t="s">
         <v>10</v>
@@ -2256,7 +2427,7 @@
         <v>84</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>195</v>
+        <v>252</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>10</v>
@@ -2279,7 +2450,7 @@
         <v>84</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>196</v>
+        <v>253</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>10</v>
@@ -2302,7 +2473,7 @@
         <v>84</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>197</v>
+        <v>254</v>
       </c>
       <c r="C57" s="2" t="s">
         <v>10</v>
@@ -2325,7 +2496,7 @@
         <v>84</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>198</v>
+        <v>255</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>10</v>
@@ -2399,7 +2570,7 @@
         <v>84</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>199</v>
+        <v>256</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>10</v>
@@ -2422,7 +2593,7 @@
         <v>84</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>200</v>
+        <v>257</v>
       </c>
       <c r="C63" s="2" t="s">
         <v>10</v>
@@ -2445,7 +2616,7 @@
         <v>84</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>201</v>
+        <v>258</v>
       </c>
       <c r="C64" s="2" t="s">
         <v>10</v>

--- a/KatalonData/RADTestData/EL-NumberValidation.xlsx
+++ b/KatalonData/RADTestData/EL-NumberValidation.xlsx
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="894" uniqueCount="202">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1008" uniqueCount="259">
   <si>
     <t>Result</t>
   </si>
@@ -643,6 +643,177 @@
   </si>
   <si>
     <t>Thu Jul 09 22:33:03 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:33:35 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:33:44 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:33:53 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:34:02 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:34:10 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:34:19 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:34:28 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:34:37 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:34:46 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:34:55 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:35:03 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:35:17 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:35:26 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:35:35 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:35:44 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:35:53 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:36:02 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:36:11 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:36:20 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:36:29 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:36:38 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:36:47 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:36:56 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:37:05 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:37:14 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:37:23 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:37:32 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:37:41 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:37:50 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:38:04 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:38:17 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:38:26 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:38:34 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:38:43 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:38:53 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:39:02 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:39:11 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:39:20 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:39:29 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:39:38 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:39:47 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:39:56 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:40:05 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:40:13 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:40:22 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:40:31 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:40:40 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:40:49 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:40:58 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:41:07 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:41:16 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:41:25 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:41:34 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:41:43 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:41:52 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:42:01 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:42:11 EDT 2026</t>
   </si>
 </sst>
 </file>
@@ -1055,7 +1226,7 @@
         <v>84</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>145</v>
+        <v>202</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>10</v>
@@ -1078,7 +1249,7 @@
         <v>84</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>146</v>
+        <v>203</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>10</v>
@@ -1101,7 +1272,7 @@
         <v>84</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>147</v>
+        <v>204</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>10</v>
@@ -1124,7 +1295,7 @@
         <v>84</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>148</v>
+        <v>205</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>10</v>
@@ -1147,7 +1318,7 @@
         <v>84</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>149</v>
+        <v>206</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>10</v>
@@ -1170,7 +1341,7 @@
         <v>84</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>150</v>
+        <v>207</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>10</v>
@@ -1193,7 +1364,7 @@
         <v>84</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>151</v>
+        <v>208</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>10</v>
@@ -1216,7 +1387,7 @@
         <v>84</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>152</v>
+        <v>209</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>10</v>
@@ -1239,7 +1410,7 @@
         <v>84</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>153</v>
+        <v>210</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>10</v>
@@ -1262,7 +1433,7 @@
         <v>84</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>154</v>
+        <v>211</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>10</v>
@@ -1285,7 +1456,7 @@
         <v>84</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>155</v>
+        <v>212</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>10</v>
@@ -1308,7 +1479,7 @@
         <v>84</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>156</v>
+        <v>213</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>10</v>
@@ -1331,7 +1502,7 @@
         <v>84</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>157</v>
+        <v>214</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>10</v>
@@ -1354,7 +1525,7 @@
         <v>84</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>158</v>
+        <v>215</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>10</v>
@@ -1377,7 +1548,7 @@
         <v>84</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>159</v>
+        <v>216</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>10</v>
@@ -1400,7 +1571,7 @@
         <v>84</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>160</v>
+        <v>217</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>10</v>
@@ -1423,7 +1594,7 @@
         <v>84</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>161</v>
+        <v>218</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>10</v>
@@ -1446,7 +1617,7 @@
         <v>84</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>162</v>
+        <v>219</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>10</v>
@@ -1469,7 +1640,7 @@
         <v>84</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>163</v>
+        <v>220</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>10</v>
@@ -1492,7 +1663,7 @@
         <v>84</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>164</v>
+        <v>221</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>10</v>
@@ -1515,7 +1686,7 @@
         <v>84</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>165</v>
+        <v>222</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>10</v>
@@ -1538,7 +1709,7 @@
         <v>84</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>166</v>
+        <v>223</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>10</v>
@@ -1561,7 +1732,7 @@
         <v>84</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>167</v>
+        <v>224</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>10</v>
@@ -1584,7 +1755,7 @@
         <v>84</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>168</v>
+        <v>225</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>10</v>
@@ -1607,7 +1778,7 @@
         <v>84</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>169</v>
+        <v>226</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>10</v>
@@ -1630,7 +1801,7 @@
         <v>84</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>170</v>
+        <v>227</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>10</v>
@@ -1653,7 +1824,7 @@
         <v>84</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>171</v>
+        <v>228</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>10</v>
@@ -1676,7 +1847,7 @@
         <v>84</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>172</v>
+        <v>229</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>10</v>
@@ -1699,7 +1870,7 @@
         <v>84</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>173</v>
+        <v>230</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>10</v>
@@ -1722,7 +1893,7 @@
         <v>84</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>174</v>
+        <v>231</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>10</v>
@@ -1745,7 +1916,7 @@
         <v>84</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>175</v>
+        <v>232</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>10</v>
@@ -1768,7 +1939,7 @@
         <v>84</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>176</v>
+        <v>233</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>10</v>
@@ -1791,7 +1962,7 @@
         <v>84</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>177</v>
+        <v>234</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>10</v>
@@ -1814,7 +1985,7 @@
         <v>84</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>178</v>
+        <v>235</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>10</v>
@@ -1837,7 +2008,7 @@
         <v>84</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>179</v>
+        <v>236</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>10</v>
@@ -1860,7 +2031,7 @@
         <v>84</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>180</v>
+        <v>237</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>10</v>
@@ -1883,7 +2054,7 @@
         <v>84</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>181</v>
+        <v>238</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>10</v>
@@ -1906,7 +2077,7 @@
         <v>84</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>182</v>
+        <v>239</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>10</v>
@@ -1929,7 +2100,7 @@
         <v>84</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>183</v>
+        <v>240</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>10</v>
@@ -2003,7 +2174,7 @@
         <v>84</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>184</v>
+        <v>241</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>10</v>
@@ -2026,7 +2197,7 @@
         <v>84</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>185</v>
+        <v>242</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>10</v>
@@ -2049,7 +2220,7 @@
         <v>84</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>186</v>
+        <v>243</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>10</v>
@@ -2072,7 +2243,7 @@
         <v>84</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>187</v>
+        <v>244</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>10</v>
@@ -2095,7 +2266,7 @@
         <v>84</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>188</v>
+        <v>245</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>10</v>
@@ -2118,7 +2289,7 @@
         <v>84</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>189</v>
+        <v>246</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>10</v>
@@ -2141,7 +2312,7 @@
         <v>84</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>190</v>
+        <v>247</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>10</v>
@@ -2164,7 +2335,7 @@
         <v>84</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>191</v>
+        <v>248</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>10</v>
@@ -2187,7 +2358,7 @@
         <v>84</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>192</v>
+        <v>249</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>10</v>
@@ -2210,7 +2381,7 @@
         <v>84</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>193</v>
+        <v>250</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>10</v>
@@ -2233,7 +2404,7 @@
         <v>84</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>194</v>
+        <v>251</v>
       </c>
       <c r="C54" s="2" t="s">
         <v>10</v>
@@ -2256,7 +2427,7 @@
         <v>84</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>195</v>
+        <v>252</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>10</v>
@@ -2279,7 +2450,7 @@
         <v>84</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>196</v>
+        <v>253</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>10</v>
@@ -2302,7 +2473,7 @@
         <v>84</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>197</v>
+        <v>254</v>
       </c>
       <c r="C57" s="2" t="s">
         <v>10</v>
@@ -2325,7 +2496,7 @@
         <v>84</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>198</v>
+        <v>255</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>10</v>
@@ -2399,7 +2570,7 @@
         <v>84</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>199</v>
+        <v>256</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>10</v>
@@ -2422,7 +2593,7 @@
         <v>84</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>200</v>
+        <v>257</v>
       </c>
       <c r="C63" s="2" t="s">
         <v>10</v>
@@ -2445,7 +2616,7 @@
         <v>84</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>201</v>
+        <v>258</v>
       </c>
       <c r="C64" s="2" t="s">
         <v>10</v>
